--- a/output/2026-09-13_03_Croazia_Varazdinska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_03_Croazia_Varazdinska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -536,7 +536,6 @@
           <t>042 204 107</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Ingrosso elementi di fissaggio, utensili, dischi abrasivi/da taglio, punte, metalli. Indirizzo Plitvička 48. Fondata 1995.</t>
@@ -665,7 +664,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pneumatica industriale, compressori, idraulica, utensili pneumatici. Fondata 1994.</t>
+          <t>Pneumatica industriale, compressori, idraulica, utensili pneumatici. Fondata 1994. [DUPLICATO — vedi anche: 2026-09-13_00_Croazia_Varazdinska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -700,7 +699,6 @@
           <t>042 232 887</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Vendita e assistenza utensili/macchine - dealer ufficiale multimarca (Bosch, Stihl, Husqvarna, Makita, Gardena). Confermato come rivenditore ufficiale Bosch Professional.</t>
@@ -745,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Attrezzature e utensili per autofficine/gommisti. Filiale operativa a Varaždin (ragione sociale titolare Autoset Turek d.o.o. ha sede a Prelog, fuori contea). Focus fortemente automotive.</t>
+          <t>Attrezzature e utensili per autofficine/gommisti. Filiale operativa a Varaždin (ragione sociale titolare Autoset Turek d.o.o. ha sede a Prelog, fuori contea). Focus fortemente automotive. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/output/2026-09-13_03_Croazia_Varazdinska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_03_Croazia_Varazdinska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-13_03_Croazia_Varazdinska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_03_Croazia_Varazdinska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tecnica di fissaggio, utensili, componenti normati - distributore gruppo RECA. Attiva dal 1996.</t>
+          <t>Tecnica di fissaggio, utensili, componenti normati - distributore gruppo RECA. Attiva dal 1996. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
